--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487983_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487983_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.0637</v>
+        <v>1.6768</v>
       </c>
       <c r="E2" t="n">
-        <v>2.3138</v>
+        <v>2.3761</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2501</v>
+        <v>-0.6993</v>
       </c>
       <c r="G2" t="n">
         <v>1.7842</v>
@@ -610,13 +610,13 @@
         <v>1.784</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.7732</v>
+        <v>-1.16</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5688</v>
+        <v>-0.5064</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2044</v>
+        <v>-0.6536</v>
       </c>
       <c r="V2" t="n">
         <v>-0.5331</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.254</v>
+        <v>-0.2639</v>
       </c>
       <c r="E3" t="n">
-        <v>1.611</v>
+        <v>0.6548</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.3571</v>
+        <v>-0.9186</v>
       </c>
       <c r="G3" t="n">
         <v>2.4861</v>
@@ -688,13 +688,13 @@
         <v>0.7929</v>
       </c>
       <c r="S3" t="n">
-        <v>1.8206</v>
+        <v>0.3027</v>
       </c>
       <c r="T3" t="n">
-        <v>1.2886</v>
+        <v>0.3323</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5319</v>
+        <v>-0.0296</v>
       </c>
       <c r="V3" t="n">
         <v>-0.674</v>
@@ -721,10 +721,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.0258</v>
+        <v>-0.3314</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0222</v>
+        <v>-0.3278</v>
       </c>
       <c r="F4" t="n">
         <v>-0.0036</v>
@@ -766,10 +766,10 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6791</v>
+        <v>0.3735</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6167</v>
+        <v>0.3111</v>
       </c>
       <c r="U4" t="n">
         <v>0.0624</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.3405</v>
+        <v>-0.3976</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2907</v>
+        <v>1.1493</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.6312</v>
+        <v>-1.5469</v>
       </c>
       <c r="G5" t="n">
         <v>1.3955</v>
@@ -844,13 +844,13 @@
         <v>1.9822</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8836000000000001</v>
+        <v>-0.9407</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1727</v>
+        <v>0.0314</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.0563</v>
+        <v>-0.9721</v>
       </c>
       <c r="V5" t="n">
         <v>0.337</v>
@@ -877,10 +877,10 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.7385</v>
+        <v>-2.9423</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4899</v>
+        <v>0.2862</v>
       </c>
       <c r="F6" t="n">
         <v>-3.2284</v>
@@ -922,10 +922,10 @@
         <v>0.5947</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1579</v>
+        <v>-0.0459</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4295</v>
+        <v>0.2258</v>
       </c>
       <c r="U6" t="n">
         <v>-0.2717</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.8043</v>
+        <v>-3.4497</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.4363</v>
+        <v>-3.3344</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.368</v>
+        <v>-0.1153</v>
       </c>
       <c r="G7" t="n">
         <v>-0.2622</v>
@@ -1000,13 +1000,13 @@
         <v>0.3964</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7492</v>
+        <v>-0.3946</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4992</v>
+        <v>-0.3973</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.25</v>
+        <v>0.0027</v>
       </c>
       <c r="V7" t="n">
         <v>-1.2071</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.7198</v>
+        <v>-3.8454</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.3933</v>
+        <v>-3.8839</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3265</v>
+        <v>0.0385</v>
       </c>
       <c r="G8" t="n">
         <v>-1.0831</v>
@@ -1078,13 +1078,13 @@
         <v>1.784</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.4562</v>
+        <v>-0.5818</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.2479</v>
+        <v>-0.7386</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2083</v>
+        <v>0.1568</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.853</v>
+        <v>-4.1865</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.8779</v>
+        <v>-2.408</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.975</v>
+        <v>-1.7785</v>
       </c>
       <c r="G9" t="n">
         <v>-0.1244</v>
@@ -1156,13 +1156,13 @@
         <v>0.7929</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.1428</v>
+        <v>-0.4763</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0072</v>
+        <v>0.4626</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.1355</v>
+        <v>-0.9389999999999999</v>
       </c>
       <c r="V9" t="n">
         <v>-1.2071</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. MIR AMATE</t>
+          <t>F. SERRANO RUBIO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.8685</v>
+        <v>-4.6445</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.6346</v>
+        <v>-3.8352</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.234</v>
+        <v>-0.8093</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.1035</v>
+        <v>0.254</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.3917</v>
+        <v>0.9601</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.7118</v>
+        <v>-0.7060999999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.331</v>
+        <v>0.074</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.7322</v>
+        <v>0.6728</v>
       </c>
       <c r="L10" t="n">
         <v>-0.5988</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.7725</v>
+        <v>0.18</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6595</v>
+        <v>0.2874</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.113</v>
+        <v>-0.1073</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.9911</v>
+        <v>-2.3787</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.1716</v>
+        <v>-2.9733</v>
       </c>
       <c r="R10" t="n">
-        <v>2.1805</v>
+        <v>0.5947</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5668</v>
+        <v>-0.6388</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.132</v>
+        <v>-0.5285</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4348</v>
+        <v>-0.1103</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.2071</v>
+        <v>-1.8811</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-0.4074</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2071</v>
+        <v>-1.4737</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>F. SERRANO RUBIO</t>
+          <t>A. MIR AMATE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.9397</v>
+        <v>-5.0203</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.2427</v>
+        <v>-4.6741</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.697</v>
+        <v>-0.3463</v>
       </c>
       <c r="G11" t="n">
-        <v>0.254</v>
+        <v>-2.1035</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9601</v>
+        <v>-1.3917</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7060999999999999</v>
+        <v>-0.7118</v>
       </c>
       <c r="J11" t="n">
-        <v>0.074</v>
+        <v>-1.331</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6728</v>
+        <v>-0.7322</v>
       </c>
       <c r="L11" t="n">
         <v>-0.5988</v>
       </c>
       <c r="M11" t="n">
-        <v>0.18</v>
+        <v>-0.7725</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2874</v>
+        <v>-0.6595</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1073</v>
+        <v>-0.113</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.3787</v>
+        <v>-0.9911</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.9733</v>
+        <v>-3.1716</v>
       </c>
       <c r="R11" t="n">
-        <v>0.5947</v>
+        <v>2.1805</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9340000000000001</v>
+        <v>-0.7186</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9360000000000001</v>
+        <v>-0.1715</v>
       </c>
       <c r="U11" t="n">
-        <v>0.002</v>
+        <v>-0.5471</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.8811</v>
+        <v>-1.2071</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.4074</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.4737</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.0474</v>
+        <v>-5.303</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.672</v>
+        <v>-3.2645</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.3755</v>
+        <v>-2.0385</v>
       </c>
       <c r="G12" t="n">
         <v>0.0391</v>
@@ -1390,13 +1390,13 @@
         <v>1.9822</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.0161</v>
+        <v>-0.2717</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6936</v>
+        <v>-0.2861</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3225</v>
+        <v>0.0145</v>
       </c>
       <c r="V12" t="n">
         <v>-3.0882</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-29.0198</v>
+        <v>-28.7078</v>
       </c>
       <c r="E13" t="n">
-        <v>-17.5736</v>
+        <v>-17.2615</v>
       </c>
       <c r="F13" t="n">
-        <v>-11.4464</v>
+        <v>-11.4462</v>
       </c>
       <c r="G13" t="n">
         <v>1.810999999999999</v>
@@ -1462,19 +1462,19 @@
         <v>-12.8845</v>
       </c>
       <c r="Q13" t="n">
-        <v>-25.7691</v>
+        <v>-25.76910000000001</v>
       </c>
       <c r="R13" t="n">
         <v>12.8845</v>
       </c>
       <c r="S13" t="n">
-        <v>-4.8643</v>
+        <v>-4.5522</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.5772</v>
+        <v>-1.2652</v>
       </c>
       <c r="U13" t="n">
-        <v>-3.2872</v>
+        <v>-3.287</v>
       </c>
       <c r="V13" t="n">
         <v>-13.082</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.8681</v>
+        <v>6.3263</v>
       </c>
       <c r="E14" t="n">
-        <v>3.9894</v>
+        <v>2.8688</v>
       </c>
       <c r="F14" t="n">
-        <v>3.8787</v>
+        <v>3.4575</v>
       </c>
       <c r="G14" t="n">
         <v>-0.1777</v>
@@ -1546,13 +1546,13 @@
         <v>3.9645</v>
       </c>
       <c r="S14" t="n">
-        <v>3.3827</v>
+        <v>1.841</v>
       </c>
       <c r="T14" t="n">
-        <v>2.4304</v>
+        <v>1.3098</v>
       </c>
       <c r="U14" t="n">
-        <v>0.9523</v>
+        <v>0.5312</v>
       </c>
       <c r="V14" t="n">
         <v>2.6808</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S. MELERO ZURITA</t>
+          <t>M. BOTAS FERNANDEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.8916</v>
+        <v>4.1672</v>
       </c>
       <c r="E15" t="n">
-        <v>1.0991</v>
+        <v>2.0373</v>
       </c>
       <c r="F15" t="n">
-        <v>2.7925</v>
+        <v>2.1299</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.9787</v>
+        <v>3.8023</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.3317</v>
+        <v>-0.5713</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.647</v>
+        <v>4.3737</v>
       </c>
       <c r="J15" t="n">
-        <v>-2.3346</v>
+        <v>5.1723</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.2687</v>
+        <v>0.8215</v>
       </c>
       <c r="L15" t="n">
-        <v>-2.0659</v>
+        <v>4.3509</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.6442</v>
+        <v>-1.37</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.0631</v>
+        <v>-1.3928</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4189</v>
+        <v>0.0228</v>
       </c>
       <c r="P15" t="n">
-        <v>2.5769</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9911</v>
+        <v>-2.9733</v>
       </c>
       <c r="R15" t="n">
-        <v>3.568</v>
+        <v>2.9733</v>
       </c>
       <c r="S15" t="n">
-        <v>1.2757</v>
+        <v>1.0389</v>
       </c>
       <c r="T15" t="n">
-        <v>0.8739</v>
+        <v>0.5123</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4018</v>
+        <v>0.5266</v>
       </c>
       <c r="V15" t="n">
-        <v>3.0178</v>
+        <v>-0.674</v>
       </c>
       <c r="W15" t="n">
-        <v>3.5509</v>
+        <v>-0.674</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.5331</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. BOTAS FERNANDEZ</t>
+          <t>P. AVALOS ORTIZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.4999</v>
+        <v>3.5834</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4261</v>
+        <v>2.6505</v>
       </c>
       <c r="F16" t="n">
-        <v>2.0738</v>
+        <v>0.9329</v>
       </c>
       <c r="G16" t="n">
-        <v>3.8023</v>
+        <v>0.6666</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.5713</v>
+        <v>-1.1471</v>
       </c>
       <c r="I16" t="n">
-        <v>4.3737</v>
+        <v>1.8137</v>
       </c>
       <c r="J16" t="n">
-        <v>5.1723</v>
+        <v>2.182</v>
       </c>
       <c r="K16" t="n">
-        <v>0.8215</v>
+        <v>0.2496</v>
       </c>
       <c r="L16" t="n">
-        <v>4.3509</v>
+        <v>1.9324</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.37</v>
+        <v>-1.5155</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.3928</v>
+        <v>-1.3967</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0228</v>
+        <v>-0.1187</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.784</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.9733</v>
+        <v>-0.9911</v>
       </c>
       <c r="R16" t="n">
-        <v>2.9733</v>
+        <v>2.7751</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3715</v>
+        <v>-0.0743</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0989</v>
+        <v>0.2525</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4704</v>
+        <v>-0.3268</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.674</v>
+        <v>1.2071</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.674</v>
+        <v>1.2071</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. VALEIRAS CREUS</t>
+          <t>S. MELERO ZURITA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.2978</v>
+        <v>3.3438</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.5716</v>
+        <v>0.6917</v>
       </c>
       <c r="F17" t="n">
-        <v>3.8694</v>
+        <v>2.6521</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7238</v>
+        <v>-2.9787</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8902</v>
+        <v>-1.3317</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1664</v>
+        <v>-1.647</v>
       </c>
       <c r="J17" t="n">
-        <v>1.1645</v>
+        <v>-2.3346</v>
       </c>
       <c r="K17" t="n">
-        <v>1.0763</v>
+        <v>-0.2687</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0881</v>
+        <v>-2.0659</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.4406</v>
+        <v>-0.6442</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1861</v>
+        <v>-1.0631</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.2545</v>
+        <v>0.4189</v>
       </c>
       <c r="P17" t="n">
-        <v>1.1893</v>
+        <v>2.5769</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9822</v>
+        <v>-0.9911</v>
       </c>
       <c r="R17" t="n">
-        <v>3.1716</v>
+        <v>3.568</v>
       </c>
       <c r="S17" t="n">
-        <v>0.9772</v>
+        <v>0.7278</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2461</v>
+        <v>0.4664</v>
       </c>
       <c r="U17" t="n">
-        <v>0.731</v>
+        <v>0.2614</v>
       </c>
       <c r="V17" t="n">
-        <v>0.4074</v>
+        <v>3.0178</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>3.5509</v>
       </c>
       <c r="X17" t="n">
-        <v>0.4074</v>
+        <v>-0.5331</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. LOPEZ PERAGON</t>
+          <t>L. SIGISMONTI RODRIGUEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.0629</v>
+        <v>3.2856</v>
       </c>
       <c r="E18" t="n">
-        <v>2.0286</v>
+        <v>1.0368</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0343</v>
+        <v>2.2488</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7428</v>
+        <v>-0.7985</v>
       </c>
       <c r="H18" t="n">
-        <v>1.5118</v>
+        <v>0.0413</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.7691</v>
+        <v>-0.8398</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3296</v>
+        <v>-0.0998</v>
       </c>
       <c r="K18" t="n">
-        <v>0.9685</v>
+        <v>0.4912</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.639</v>
+        <v>-0.591</v>
       </c>
       <c r="M18" t="n">
-        <v>0.4132</v>
+        <v>-0.6987</v>
       </c>
       <c r="N18" t="n">
-        <v>0.5433</v>
+        <v>-0.4499</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1301</v>
+        <v>-0.2488</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9911</v>
+        <v>2.5769</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9911</v>
+        <v>2.5769</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1219</v>
+        <v>0.3001</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4919</v>
+        <v>-0.07049999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.37</v>
+        <v>0.3706</v>
       </c>
       <c r="V18" t="n">
         <v>1.2071</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. AVALOS ORTIZ</t>
+          <t>J. VALEIRAS CREUS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.3296</v>
+        <v>2.8694</v>
       </c>
       <c r="E19" t="n">
-        <v>1.7337</v>
+        <v>-0.7754</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5959</v>
+        <v>3.6447</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6666</v>
+        <v>0.7238</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.1471</v>
+        <v>0.8902</v>
       </c>
       <c r="I19" t="n">
-        <v>1.8137</v>
+        <v>-0.1664</v>
       </c>
       <c r="J19" t="n">
-        <v>2.182</v>
+        <v>1.1645</v>
       </c>
       <c r="K19" t="n">
-        <v>0.2496</v>
+        <v>1.0763</v>
       </c>
       <c r="L19" t="n">
-        <v>1.9324</v>
+        <v>0.0881</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.5155</v>
+        <v>-0.4406</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.3967</v>
+        <v>-0.1861</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1187</v>
+        <v>-0.2545</v>
       </c>
       <c r="P19" t="n">
-        <v>1.784</v>
+        <v>1.1893</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9911</v>
+        <v>-1.9822</v>
       </c>
       <c r="R19" t="n">
-        <v>2.7751</v>
+        <v>3.1716</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.3281</v>
+        <v>0.5488</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6643</v>
+        <v>0.0424</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6637999999999999</v>
+        <v>0.5064</v>
       </c>
       <c r="V19" t="n">
-        <v>1.2071</v>
+        <v>0.4074</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2071</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>0.4074</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>L. SIGISMONTI RODRIGUEZ</t>
+          <t>M. LOPEZ PERAGON</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.2564</v>
+        <v>2.8134</v>
       </c>
       <c r="E20" t="n">
-        <v>0.12</v>
+        <v>1.723</v>
       </c>
       <c r="F20" t="n">
-        <v>2.1365</v>
+        <v>1.0904</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.7985</v>
+        <v>0.7428</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0413</v>
+        <v>1.5118</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.8398</v>
+        <v>-0.7691</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.0998</v>
+        <v>0.3296</v>
       </c>
       <c r="K20" t="n">
-        <v>0.4912</v>
+        <v>0.9685</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.591</v>
+        <v>-0.639</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.6987</v>
+        <v>0.4132</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4499</v>
+        <v>0.5433</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2488</v>
+        <v>-0.1301</v>
       </c>
       <c r="P20" t="n">
-        <v>2.5769</v>
+        <v>0.9911</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.5769</v>
+        <v>0.9911</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.729</v>
+        <v>-0.1276</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9873</v>
+        <v>0.1863</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2583</v>
+        <v>-0.3139</v>
       </c>
       <c r="V20" t="n">
         <v>1.2071</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>L. SIGISMONTI RODRÍGUEZ</t>
+          <t>R. REVELLES DIAZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.508</v>
+        <v>2.67</v>
       </c>
       <c r="E21" t="n">
-        <v>1.508</v>
+        <v>-0.2236</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>2.8936</v>
       </c>
       <c r="G21" t="n">
-        <v>1.508</v>
+        <v>-2.0424</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3027</v>
+        <v>-1.9488</v>
       </c>
       <c r="I21" t="n">
-        <v>1.2053</v>
+        <v>-0.0936</v>
       </c>
       <c r="J21" t="n">
-        <v>1.508</v>
+        <v>-1.7319</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3027</v>
+        <v>-1.6269</v>
       </c>
       <c r="L21" t="n">
-        <v>1.2053</v>
+        <v>-0.105</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>-0.3105</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>0.0114</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.1805</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>3.1716</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>-0.2193</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>-0.5183</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>0.2991</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>2.7512</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>3.0178</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R. REVELLES DIAZ</t>
+          <t>L. SIGISMONTI RODRÍGUEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1.4724</v>
+        <v>1.508</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.1404</v>
+        <v>1.508</v>
       </c>
       <c r="F22" t="n">
-        <v>2.6128</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.0424</v>
+        <v>1.508</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.9488</v>
+        <v>0.3027</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.0936</v>
+        <v>1.2053</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.7319</v>
+        <v>1.508</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.6269</v>
+        <v>0.3027</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.105</v>
+        <v>1.2053</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.3105</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>0.0114</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.1805</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>3.1716</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.4169</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.4351</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0183</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>2.7512</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>3.0178</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.2666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2024</v>
+        <v>-1.0663</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.1919</v>
+        <v>-0.8031</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.0105</v>
+        <v>-0.2632</v>
       </c>
       <c r="G24" t="n">
         <v>-3.7873</v>
@@ -2326,13 +2326,13 @@
         <v>1.9822</v>
       </c>
       <c r="S24" t="n">
-        <v>1.8248</v>
+        <v>0.9609</v>
       </c>
       <c r="T24" t="n">
-        <v>1.4979</v>
+        <v>0.8867</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3269</v>
+        <v>0.0742</v>
       </c>
       <c r="V24" t="n">
         <v>2.7512</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.5697</v>
+        <v>-1.0862</v>
       </c>
       <c r="E25" t="n">
-        <v>0.8399</v>
+        <v>0.1268</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.4096</v>
+        <v>-1.2131</v>
       </c>
       <c r="G25" t="n">
         <v>-0.0751</v>
@@ -2404,13 +2404,13 @@
         <v>0.5947</v>
       </c>
       <c r="S25" t="n">
-        <v>0.3844</v>
+        <v>-0.1321</v>
       </c>
       <c r="T25" t="n">
-        <v>0.9325</v>
+        <v>0.2194</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.5481</v>
+        <v>-0.3515</v>
       </c>
       <c r="V25" t="n">
         <v>-1.4737</v>
@@ -2440,10 +2440,10 @@
         <v>29.0199</v>
       </c>
       <c r="E26" t="n">
-        <v>11.4462</v>
+        <v>11.4461</v>
       </c>
       <c r="F26" t="n">
-        <v>17.5738</v>
+        <v>17.5736</v>
       </c>
       <c r="G26" t="n">
         <v>-1.810900000000001</v>
@@ -2455,16 +2455,16 @@
         <v>3.9323</v>
       </c>
       <c r="J26" t="n">
-        <v>4.621900000000001</v>
+        <v>4.6219</v>
       </c>
       <c r="K26" t="n">
-        <v>1.511400000000001</v>
+        <v>1.5114</v>
       </c>
       <c r="L26" t="n">
-        <v>3.1104</v>
+        <v>3.110399999999999</v>
       </c>
       <c r="M26" t="n">
-        <v>-6.432900000000001</v>
+        <v>-6.4329</v>
       </c>
       <c r="N26" t="n">
         <v>-7.2546</v>
@@ -2482,13 +2482,13 @@
         <v>25.769</v>
       </c>
       <c r="S26" t="n">
-        <v>4.8642</v>
+        <v>4.864199999999999</v>
       </c>
       <c r="T26" t="n">
-        <v>3.287100000000001</v>
+        <v>3.286999999999999</v>
       </c>
       <c r="U26" t="n">
-        <v>1.5771</v>
+        <v>1.5773</v>
       </c>
       <c r="V26" t="n">
         <v>13.082</v>
